--- a/InputData/ctrl-settings/BUCMfNCR/Boolean Use Capacity Market for New Capacity Revenue.xlsx
+++ b/InputData/ctrl-settings/BUCMfNCR/Boolean Use Capacity Market for New Capacity Revenue.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\ctrl-settings\BUCMfNCR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-india\InputData\ctrl-settings\BUCMfNCR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FAB3BCE-99C1-487F-AB05-5C4B12C50D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E5C8D5-DD99-4231-89D1-E4C79002EA27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32790" yWindow="3990" windowWidth="21600" windowHeight="12525" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -391,39 +391,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -439,14 +439,14 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
